--- a/config/generated/templates/ModifierDefinition.xlsx
+++ b/config/generated/templates/ModifierDefinition.xlsx
@@ -902,8 +902,8 @@
     </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Hp, Atk, Def, Spd, CritRate, CritDamage, EffectHitRate, EffectResistance, BreakEffect, EnergyRegenerationRate, OutgoingHealing, IncomingHealing, ShieldStrength, Aggro, ToughnessDamage" promptTitle="StatKind enum" prompt="Select a value from the dropdown." sqref="G8:G1007">
-      <formula1>"Hp,Atk,Def,Spd,CritRate,CritDamage,EffectHitRate,EffectResistance,BreakEffect,EnergyRegenerationRate,OutgoingHealing,IncomingHealing,ShieldStrength,Aggro,ToughnessDamage"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Hp, Atk, Def, Spd, CritRate, CritDamage, EffectHitRate, EffectResistance, BreakEffect, EnergyRegenerationRate, OutgoingHealing, IncomingHealing, ShieldStrength, Aggro, ToughnessDamage, Elation" promptTitle="StatKind enum" prompt="Select a value from the dropdown." sqref="G8:G1007">
+      <formula1>"Hp,Atk,Def,Spd,CritRate,CritDamage,EffectHitRate,EffectResistance,BreakEffect,EnergyRegenerationRate,OutgoingHealing,IncomingHealing,ShieldStrength,Aggro,ToughnessDamage,Elation"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: BaseAdd, PercentOfBase, Flat, FinalAdd, FinalMultiply, Crit, DamageBoost, Weaken, Defense, Resistance, Vulnerability, Mitigation, Broken, Healing, Shield, Probability" promptTitle="FormulaStage enum" prompt="Select a value from the dropdown." sqref="H8:H1007">
       <formula1>"BaseAdd,PercentOfBase,Flat,FinalAdd,FinalMultiply,Crit,DamageBoost,Weaken,Defense,Resistance,Vulnerability,Mitigation,Broken,Healing,Shield,Probability"</formula1>
